--- a/college-posters/data/字段表_北京理工大学样板.xlsx
+++ b/college-posters/data/字段表_北京理工大学样板.xlsx
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>软科 BCUR 2026（媒体转载，多源一致）</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>待核软科官网</t>
+          <t>软科 BCUR 2026（高考100总榜等转载，多源一致）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>已核（多源一致；软科官网未能直连）</t>
         </is>
       </c>
     </row>
@@ -1332,22 +1332,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2026年全球第259名</t>
+          <t>2027年全球第243名，首次进入前250（2026年第259名）</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>259名（2026）</t>
+          <t>243名（2027）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>北理工国际学生招生简章 isc.bit.edu.cn</t>
+          <t>IT之家 QS 2027 发布报道、苏大图书馆整理</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>已核；QS 2027 已发布，名次待查</t>
+          <t>已核（多源一致）</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2025年全球101–150区间</t>
+          <t>2025年全球第102名（101–150区间）；2026年名次未查到</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>公开报道</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>待核 ARWU 官网</t>
+          <t>北理工国际学生招生简章 isc.bit.edu.cn</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2025已核；2026名次待查</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>学校官网、公开资料</t>
+          <t>北理工英文官网 About BIT、公开资料</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1952年（另有资料作1951年）待核官网校史</t>
+          <t>已核（1952年定名北京工业学院）</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2023–2024学年本科教学质量报告（转载）</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>待核报告原文</t>
+          <t>2023–2024学年本科教学质量报告（自主选拔在线、搜狐转载，数字一致）</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（多源一致，原文未能直连）</t>
         </is>
       </c>
     </row>
@@ -1812,22 +1812,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>工科 / 理科试验班：物理 + 化学；社会科学试验班：要求较宽</t>
+          <t>2026年分省计划：物理类专业均要求物理+化学；历史类社会科学试验班为历史+不限；中外合作会计学（甘肃）物理+不限</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>理工类 物理+化学；人文社科类 以当年章程为准</t>
+          <t>理工类 物理+化学；社科试验班（历史类）历史+不限</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划（转载）</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生章程</t>
+          <t>2026年分省招生计划（转载）、2026年招生章程</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>已核（2026年）；2027年以新章程为准</t>
         </is>
       </c>
     </row>

--- a/college-posters/data/字段表_北京理工大学样板.xlsx
+++ b/college-posters/data/字段表_北京理工大学样板.xlsx
@@ -1172,12 +1172,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>中国共产党创办的第一所理工科大学，前身为1940年延安自然科学院</t>
+          <t>前身为1940年创办的延安自然科学院，从延安窑洞走出的理工名校</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>中国共产党创办的第一所理工科大学</t>
+          <t>从延安窑洞走出的理工名校</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
